--- a/kvcache/unified_kv_memory/统一异构KVCache存储池_全量需求树_V2.3.1_SR项目贡献补充版.xlsx
+++ b/kvcache/unified_kv_memory/统一异构KVCache存储池_全量需求树_V2.3.1_SR项目贡献补充版.xlsx
@@ -6774,7 +6774,7 @@
       </c>
       <c r="Y22" s="36" t="inlineStr">
         <is>
-          <t>模块功能闭包｜按实际路径形成完整性证据、RAS 故障映射和阻断规则；为第一方问题归因、错误消费防护和跨版本认证提供可审计依据。</t>
+          <t>模块功能闭包｜按实际路径形成完整性证据、RAS 故障映射和阻断规则；为原厂系统问题归因、错误消费防护和跨版本认证提供可审计依据。</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Y37" s="36" t="inlineStr">
         <is>
-          <t>模块功能闭包｜交付链路追踪、回退分析和 KV 检查（KVInspect）工具；缩短跨框架、传输、驱动与硬件的问题定位路径，形成第一方责任闭环。</t>
+          <t>模块功能闭包｜交付链路追踪、回退分析和 KV 检查（KVInspect）工具；缩短跨框架、传输、驱动与硬件的问题定位路径，形成原厂软硬件协同系统责任闭环。</t>
         </is>
       </c>
     </row>
